--- a/eval-runner/orchestrator/data/EE/07_stage2/EE_본판정_판정대장_13_v1_0.xlsx
+++ b/eval-runner/orchestrator/data/EE/07_stage2/EE_본판정_판정대장_13_v1_0.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>판정</t>
+          <t>판정(채점관 Kimi)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,7 +439,32 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>검토 판정(claude 새 세션)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>검토 판정문</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>불일치</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>재검 대상</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>최종 판정</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>사람 개입</t>
         </is>
       </c>
     </row>
@@ -464,7 +489,24 @@
           <t>EE-A01: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EE-A01: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -487,7 +529,24 @@
           <t>EE-A02: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EE-A02: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -510,7 +569,24 @@
           <t>EE-A03: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>EE-A03: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -533,7 +609,24 @@
           <t>EE-F04: 정답 필수 요소 대조 — 부분. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EE-F04: 정답 필수 요소 대조 — 부분. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -556,7 +649,24 @@
           <t>EE-F05: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>EE-F05: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -579,7 +689,24 @@
           <t>EE-A06: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>EE-A06: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -602,7 +729,24 @@
           <t>EE-G07: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EE-G07: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -625,7 +769,24 @@
           <t>EE-A08: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>EE-A08: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -648,7 +809,24 @@
           <t>EE-F09: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>EE-F09: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -671,7 +849,24 @@
           <t>EE-C10: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>EE-C10: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -694,7 +889,24 @@
           <t>EE-G11: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>EE-G11: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -719,9 +931,26 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>EE-C12: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -744,7 +973,24 @@
           <t>EE-E13: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>EE-E13: 정답 필수 요소 대조 — 합격. 근거 출처 실재 확인.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
